--- a/data/chart_statistics.xlsx
+++ b/data/chart_statistics.xlsx
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>763</v>
+        <v>531</v>
       </c>
     </row>
     <row r="3">
@@ -642,7 +642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
@@ -739,7 +739,7 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
@@ -754,7 +754,7 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>45</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10">
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13">
@@ -844,7 +844,7 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -859,142 +859,7 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>1220</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>台榮</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>1225</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>福懋油</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>1227</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>佳格</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>1229</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>聯華</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>1231</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>聯華食</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>1232</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>大統益</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>1233</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>天仁</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>1234</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>黑松</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>1235</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>興泰</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="n">
-        <v>33</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
